--- a/public/downloads/Anexos/Ejemplo_1_calculo_y_grafico.xlsx
+++ b/public/downloads/Anexos/Ejemplo_1_calculo_y_grafico.xlsx
@@ -4011,13 +4011,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B51BB95-0514-4EF7-97CB-25F0C2F1BF86}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2870C094-6D43-4305-A6AE-7FE00CD0D932}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51B3CDFF-178D-4995-955B-7EF505B0E6E5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1268583A-85F7-4DA8-8B34-7EA4BD1DA09B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F54D992F-BC03-4BC0-BB54-9791038268A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84A025C9-695E-481F-B3AE-6B57300272F2}"/>
 </file>